--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G21">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G45">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G62">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G69">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G21">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G46">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G46">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,69 +6336,69 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P37">
+        <v>5.15</v>
+      </c>
+      <c r="Q37">
+        <v>2.19</v>
+      </c>
+      <c r="R37">
+        <v>2.23</v>
+      </c>
+      <c r="S37">
+        <v>1.3</v>
+      </c>
+      <c r="T37">
+        <v>3.2</v>
+      </c>
+      <c r="U37">
+        <v>2.4</v>
+      </c>
+      <c r="V37">
+        <v>1.5</v>
+      </c>
+      <c r="W37">
+        <v>1.07</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.19</v>
+      </c>
+      <c r="Z37">
+        <v>3.8</v>
+      </c>
+      <c r="AA37">
+        <v>1.73</v>
+      </c>
+      <c r="AB37">
+        <v>2.15</v>
+      </c>
+      <c r="AC37">
+        <v>2.61</v>
+      </c>
+      <c r="AD37">
+        <v>1.39</v>
+      </c>
+      <c r="AE37">
+        <v>1.12</v>
+      </c>
+      <c r="AF37">
+        <v>1.73</v>
+      </c>
+      <c r="AG37">
         <v>2</v>
       </c>
-      <c r="Q37">
-        <v>3.9</v>
-      </c>
-      <c r="R37">
-        <v>2.25</v>
-      </c>
-      <c r="S37">
-        <v>1.38</v>
-      </c>
-      <c r="T37">
-        <v>3.08</v>
-      </c>
-      <c r="U37">
-        <v>2.78</v>
-      </c>
-      <c r="V37">
-        <v>1.43</v>
-      </c>
-      <c r="W37">
-        <v>1.06</v>
-      </c>
-      <c r="X37">
-        <v>1.05</v>
-      </c>
-      <c r="Y37">
-        <v>1.27</v>
-      </c>
-      <c r="Z37">
-        <v>3.7</v>
-      </c>
-      <c r="AA37">
-        <v>1.86</v>
-      </c>
-      <c r="AB37">
-        <v>1.91</v>
-      </c>
-      <c r="AC37">
-        <v>3.16</v>
-      </c>
-      <c r="AD37">
-        <v>1.31</v>
-      </c>
-      <c r="AE37">
-        <v>1.07</v>
-      </c>
-      <c r="AF37">
-        <v>1.7</v>
-      </c>
-      <c r="AG37">
-        <v>2.05</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,84 +6499,84 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>5.15</v>
+        <v>2</v>
       </c>
       <c r="Q38">
-        <v>2.19</v>
+        <v>3.9</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1.05</v>
+      </c>
+      <c r="Y38">
+        <v>1.27</v>
+      </c>
+      <c r="Z38">
+        <v>3.7</v>
+      </c>
+      <c r="AA38">
+        <v>1.86</v>
+      </c>
+      <c r="AB38">
+        <v>1.91</v>
+      </c>
+      <c r="AC38">
+        <v>3.16</v>
+      </c>
+      <c r="AD38">
+        <v>1.31</v>
+      </c>
+      <c r="AE38">
         <v>1.07</v>
       </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.19</v>
-      </c>
-      <c r="Z38">
-        <v>3.8</v>
-      </c>
-      <c r="AA38">
+      <c r="AF38">
+        <v>1.7</v>
+      </c>
+      <c r="AG38">
+        <v>2.05</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.73</v>
       </c>
-      <c r="AB38">
-        <v>2.15</v>
-      </c>
-      <c r="AC38">
-        <v>2.61</v>
-      </c>
-      <c r="AD38">
-        <v>1.39</v>
-      </c>
-      <c r="AE38">
-        <v>1.12</v>
-      </c>
-      <c r="AF38">
-        <v>1.73</v>
-      </c>
-      <c r="AG38">
-        <v>2</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.25</v>
-      </c>
       <c r="AK38">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G46">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G21">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G33">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G21">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G33">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,84 +6336,84 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>5.15</v>
+        <v>2</v>
       </c>
       <c r="Q37">
-        <v>2.19</v>
+        <v>3.9</v>
       </c>
       <c r="R37">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W37">
+        <v>1.06</v>
+      </c>
+      <c r="X37">
+        <v>1.05</v>
+      </c>
+      <c r="Y37">
+        <v>1.27</v>
+      </c>
+      <c r="Z37">
+        <v>3.7</v>
+      </c>
+      <c r="AA37">
+        <v>1.86</v>
+      </c>
+      <c r="AB37">
+        <v>1.91</v>
+      </c>
+      <c r="AC37">
+        <v>3.16</v>
+      </c>
+      <c r="AD37">
+        <v>1.31</v>
+      </c>
+      <c r="AE37">
         <v>1.07</v>
       </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.19</v>
-      </c>
-      <c r="Z37">
-        <v>3.8</v>
-      </c>
-      <c r="AA37">
+      <c r="AF37">
+        <v>1.7</v>
+      </c>
+      <c r="AG37">
+        <v>2.05</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.73</v>
       </c>
-      <c r="AB37">
-        <v>2.15</v>
-      </c>
-      <c r="AC37">
-        <v>2.61</v>
-      </c>
-      <c r="AD37">
-        <v>1.39</v>
-      </c>
-      <c r="AE37">
-        <v>1.12</v>
-      </c>
-      <c r="AF37">
-        <v>1.73</v>
-      </c>
-      <c r="AG37">
-        <v>2</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.25</v>
-      </c>
       <c r="AK37">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,69 +6499,69 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P38">
+        <v>5.15</v>
+      </c>
+      <c r="Q38">
+        <v>2.19</v>
+      </c>
+      <c r="R38">
+        <v>2.23</v>
+      </c>
+      <c r="S38">
+        <v>1.3</v>
+      </c>
+      <c r="T38">
+        <v>3.2</v>
+      </c>
+      <c r="U38">
+        <v>2.4</v>
+      </c>
+      <c r="V38">
+        <v>1.5</v>
+      </c>
+      <c r="W38">
+        <v>1.07</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
+        <v>1.19</v>
+      </c>
+      <c r="Z38">
+        <v>3.8</v>
+      </c>
+      <c r="AA38">
+        <v>1.73</v>
+      </c>
+      <c r="AB38">
+        <v>2.15</v>
+      </c>
+      <c r="AC38">
+        <v>2.61</v>
+      </c>
+      <c r="AD38">
+        <v>1.39</v>
+      </c>
+      <c r="AE38">
+        <v>1.12</v>
+      </c>
+      <c r="AF38">
+        <v>1.73</v>
+      </c>
+      <c r="AG38">
         <v>2</v>
       </c>
-      <c r="Q38">
-        <v>3.9</v>
-      </c>
-      <c r="R38">
-        <v>2.25</v>
-      </c>
-      <c r="S38">
-        <v>1.38</v>
-      </c>
-      <c r="T38">
-        <v>3.08</v>
-      </c>
-      <c r="U38">
-        <v>2.78</v>
-      </c>
-      <c r="V38">
-        <v>1.43</v>
-      </c>
-      <c r="W38">
-        <v>1.06</v>
-      </c>
-      <c r="X38">
-        <v>1.05</v>
-      </c>
-      <c r="Y38">
-        <v>1.27</v>
-      </c>
-      <c r="Z38">
-        <v>3.7</v>
-      </c>
-      <c r="AA38">
-        <v>1.86</v>
-      </c>
-      <c r="AB38">
-        <v>1.91</v>
-      </c>
-      <c r="AC38">
-        <v>3.16</v>
-      </c>
-      <c r="AD38">
-        <v>1.31</v>
-      </c>
-      <c r="AE38">
-        <v>1.07</v>
-      </c>
-      <c r="AF38">
-        <v>1.7</v>
-      </c>
-      <c r="AG38">
-        <v>2.05</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G46">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU71"/>
+  <dimension ref="A1:AU72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G12">
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-15 16:30:00</t>
+          <t>2026-09-15 16:15:00</t>
         </is>
       </c>
     </row>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-15 18:00:00</t>
+          <t>2026-09-15 16:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:00</t>
+          <t>2026-09-15 18:00:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-15 19:30:00</t>
+          <t>2026-09-15 18:15:00</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G51">
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G52">
@@ -8781,68 +8781,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-15 20:00:00</t>
+          <t>2026-09-15 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.65</v>
+        <v>5.25</v>
       </c>
       <c r="O53">
-        <v>3.98</v>
+        <v>3.45</v>
       </c>
       <c r="P53">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="Q53">
-        <v>2.11</v>
+        <v>5.8</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="T53">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="U53">
-        <v>2.24</v>
+        <v>3.12</v>
       </c>
       <c r="V53">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="W53">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="Z53">
-        <v>4.45</v>
+        <v>2.83</v>
       </c>
       <c r="AA53">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AB53">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC53">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD53">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AE53">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>2.1</v>
+        <v>1.15</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G54">
@@ -9107,68 +9107,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-09-15 20:30:00</t>
+          <t>2026-09-15 20:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-09-15 21:00:00</t>
+          <t>2026-09-15 20:30:00</t>
         </is>
       </c>
     </row>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G63">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,151 +11840,314 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Napredak</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>OFK Vršac</t>
+        </is>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71">
+        <v>0</v>
+      </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>0</v>
+      </c>
+      <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71" t="inlineStr">
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>0</v>
-      </c>
-      <c r="T71">
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <v>0</v>
-      </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
-      <c r="W71">
-        <v>0</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>0</v>
-      </c>
-      <c r="Z71">
-        <v>0</v>
-      </c>
-      <c r="AA71">
-        <v>0</v>
-      </c>
-      <c r="AB71">
-        <v>0</v>
-      </c>
-      <c r="AC71">
-        <v>0</v>
-      </c>
-      <c r="AD71">
-        <v>0</v>
-      </c>
-      <c r="AE71">
-        <v>0</v>
-      </c>
-      <c r="AF71">
-        <v>0</v>
-      </c>
-      <c r="AG71">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>0</v>
-      </c>
-      <c r="AK71">
-        <v>0</v>
-      </c>
-      <c r="AL71">
-        <v>0</v>
-      </c>
-      <c r="AM71">
-        <v>-1</v>
-      </c>
-      <c r="AN71">
-        <v>-1</v>
-      </c>
-      <c r="AO71">
-        <v>-1</v>
-      </c>
-      <c r="AP71">
-        <v>-1</v>
-      </c>
-      <c r="AQ71">
-        <v>0</v>
-      </c>
-      <c r="AR71">
-        <v>0</v>
-      </c>
-      <c r="AS71">
-        <v>0</v>
-      </c>
-      <c r="AT71">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>0</v>
+      </c>
+      <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>-1</v>
+      </c>
+      <c r="AN72">
+        <v>-1</v>
+      </c>
+      <c r="AO72">
+        <v>-1</v>
+      </c>
+      <c r="AP72">
+        <v>-1</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>0</v>
+      </c>
+      <c r="AS72">
+        <v>0</v>
+      </c>
+      <c r="AT72">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
         <is>
           <t>2026-09-15 21:00:00</t>
         </is>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU72"/>
+  <dimension ref="A1:AU63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>5.25</v>
+        <v>1.65</v>
       </c>
       <c r="O53">
-        <v>3.45</v>
+        <v>3.98</v>
       </c>
       <c r="P53">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="Q53">
-        <v>5.8</v>
+        <v>2.11</v>
       </c>
       <c r="R53">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="U53">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="V53">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>2.83</v>
+        <v>4.45</v>
       </c>
       <c r="AA53">
+        <v>1.62</v>
+      </c>
+      <c r="AB53">
         <v>2.2</v>
       </c>
-      <c r="AB53">
-        <v>1.6</v>
-      </c>
       <c r="AC53">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD53">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AE53">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AF53">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK53">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G54">
@@ -9107,68 +9107,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK54">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-09-15 20:00:00</t>
+          <t>2026-09-15 20:30:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-09-15 20:30:00</t>
+          <t>2026-09-15 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G63">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63">
@@ -10681,1473 +10681,6 @@
         <v>0</v>
       </c>
       <c r="AU63" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
-      </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>0</v>
-      </c>
-      <c r="AB64">
-        <v>0</v>
-      </c>
-      <c r="AC64">
-        <v>0</v>
-      </c>
-      <c r="AD64">
-        <v>0</v>
-      </c>
-      <c r="AE64">
-        <v>0</v>
-      </c>
-      <c r="AF64">
-        <v>0</v>
-      </c>
-      <c r="AG64">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>0</v>
-      </c>
-      <c r="AK64">
-        <v>0</v>
-      </c>
-      <c r="AL64">
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <v>-1</v>
-      </c>
-      <c r="AN64">
-        <v>-1</v>
-      </c>
-      <c r="AO64">
-        <v>-1</v>
-      </c>
-      <c r="AP64">
-        <v>-1</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <v>-1</v>
-      </c>
-      <c r="AN65">
-        <v>-1</v>
-      </c>
-      <c r="AO65">
-        <v>-1</v>
-      </c>
-      <c r="AP65">
-        <v>-1</v>
-      </c>
-      <c r="AQ65">
-        <v>0</v>
-      </c>
-      <c r="AR65">
-        <v>0</v>
-      </c>
-      <c r="AS65">
-        <v>0</v>
-      </c>
-      <c r="AT65">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
-      </c>
-      <c r="AE66">
-        <v>0</v>
-      </c>
-      <c r="AF66">
-        <v>0</v>
-      </c>
-      <c r="AG66">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>0</v>
-      </c>
-      <c r="AK66">
-        <v>0</v>
-      </c>
-      <c r="AL66">
-        <v>0</v>
-      </c>
-      <c r="AM66">
-        <v>-1</v>
-      </c>
-      <c r="AN66">
-        <v>-1</v>
-      </c>
-      <c r="AO66">
-        <v>-1</v>
-      </c>
-      <c r="AP66">
-        <v>-1</v>
-      </c>
-      <c r="AQ66">
-        <v>0</v>
-      </c>
-      <c r="AR66">
-        <v>0</v>
-      </c>
-      <c r="AS66">
-        <v>0</v>
-      </c>
-      <c r="AT66">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>0</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>0</v>
-      </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>0</v>
-      </c>
-      <c r="AB68">
-        <v>0</v>
-      </c>
-      <c r="AC68">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>0</v>
-      </c>
-      <c r="AE68">
-        <v>0</v>
-      </c>
-      <c r="AF68">
-        <v>0</v>
-      </c>
-      <c r="AG68">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>0</v>
-      </c>
-      <c r="AK68">
-        <v>0</v>
-      </c>
-      <c r="AL68">
-        <v>0</v>
-      </c>
-      <c r="AM68">
-        <v>-1</v>
-      </c>
-      <c r="AN68">
-        <v>-1</v>
-      </c>
-      <c r="AO68">
-        <v>-1</v>
-      </c>
-      <c r="AP68">
-        <v>-1</v>
-      </c>
-      <c r="AQ68">
-        <v>0</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
-        <v>0</v>
-      </c>
-      <c r="AT68">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
-        <v>0</v>
-      </c>
-      <c r="AC69">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>0</v>
-      </c>
-      <c r="AE69">
-        <v>0</v>
-      </c>
-      <c r="AF69">
-        <v>0</v>
-      </c>
-      <c r="AG69">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>0</v>
-      </c>
-      <c r="AK69">
-        <v>0</v>
-      </c>
-      <c r="AL69">
-        <v>0</v>
-      </c>
-      <c r="AM69">
-        <v>-1</v>
-      </c>
-      <c r="AN69">
-        <v>-1</v>
-      </c>
-      <c r="AO69">
-        <v>-1</v>
-      </c>
-      <c r="AP69">
-        <v>-1</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>0</v>
-      </c>
-      <c r="Y70">
-        <v>0</v>
-      </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>0</v>
-      </c>
-      <c r="AB70">
-        <v>0</v>
-      </c>
-      <c r="AC70">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>0</v>
-      </c>
-      <c r="AE70">
-        <v>0</v>
-      </c>
-      <c r="AF70">
-        <v>0</v>
-      </c>
-      <c r="AG70">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>0</v>
-      </c>
-      <c r="AK70">
-        <v>0</v>
-      </c>
-      <c r="AL70">
-        <v>0</v>
-      </c>
-      <c r="AM70">
-        <v>-1</v>
-      </c>
-      <c r="AN70">
-        <v>-1</v>
-      </c>
-      <c r="AO70">
-        <v>-1</v>
-      </c>
-      <c r="AP70">
-        <v>-1</v>
-      </c>
-      <c r="AQ70">
-        <v>0</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
-        <v>0</v>
-      </c>
-      <c r="AT70">
-        <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>0</v>
-      </c>
-      <c r="T71">
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <v>0</v>
-      </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
-      <c r="W71">
-        <v>0</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>0</v>
-      </c>
-      <c r="Z71">
-        <v>0</v>
-      </c>
-      <c r="AA71">
-        <v>0</v>
-      </c>
-      <c r="AB71">
-        <v>0</v>
-      </c>
-      <c r="AC71">
-        <v>0</v>
-      </c>
-      <c r="AD71">
-        <v>0</v>
-      </c>
-      <c r="AE71">
-        <v>0</v>
-      </c>
-      <c r="AF71">
-        <v>0</v>
-      </c>
-      <c r="AG71">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>0</v>
-      </c>
-      <c r="AK71">
-        <v>0</v>
-      </c>
-      <c r="AL71">
-        <v>0</v>
-      </c>
-      <c r="AM71">
-        <v>-1</v>
-      </c>
-      <c r="AN71">
-        <v>-1</v>
-      </c>
-      <c r="AO71">
-        <v>-1</v>
-      </c>
-      <c r="AP71">
-        <v>-1</v>
-      </c>
-      <c r="AQ71">
-        <v>0</v>
-      </c>
-      <c r="AR71">
-        <v>0</v>
-      </c>
-      <c r="AS71">
-        <v>0</v>
-      </c>
-      <c r="AT71">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Sport Recife</t>
-        </is>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>0</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <v>0</v>
-      </c>
-      <c r="V72">
-        <v>0</v>
-      </c>
-      <c r="W72">
-        <v>0</v>
-      </c>
-      <c r="X72">
-        <v>0</v>
-      </c>
-      <c r="Y72">
-        <v>0</v>
-      </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <v>0</v>
-      </c>
-      <c r="AB72">
-        <v>0</v>
-      </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <v>0</v>
-      </c>
-      <c r="AE72">
-        <v>0</v>
-      </c>
-      <c r="AF72">
-        <v>0</v>
-      </c>
-      <c r="AG72">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>0</v>
-      </c>
-      <c r="AK72">
-        <v>0</v>
-      </c>
-      <c r="AL72">
-        <v>0</v>
-      </c>
-      <c r="AM72">
-        <v>-1</v>
-      </c>
-      <c r="AN72">
-        <v>-1</v>
-      </c>
-      <c r="AO72">
-        <v>-1</v>
-      </c>
-      <c r="AP72">
-        <v>-1</v>
-      </c>
-      <c r="AQ72">
-        <v>0</v>
-      </c>
-      <c r="AR72">
-        <v>0</v>
-      </c>
-      <c r="AS72">
-        <v>0</v>
-      </c>
-      <c r="AT72">
-        <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
         <is>
           <t>2026-09-15 21:00:00</t>
         </is>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G61">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G2">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G21">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37">
-        <v>3.4</v>
+        <v>2.02</v>
       </c>
       <c r="O37">
         <v>3.4</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="V37">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA37">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="AD37">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="AK37">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="O39">
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="Q39">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="R39">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U39">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z39">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA39">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AB39">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC39">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="AD39">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="AK39">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2612,43 +2612,43 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2938,43 +2938,43 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,84 +6499,84 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>5.15</v>
+        <v>2</v>
       </c>
       <c r="Q38">
-        <v>2.19</v>
+        <v>3.9</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1.05</v>
+      </c>
+      <c r="Y38">
+        <v>1.27</v>
+      </c>
+      <c r="Z38">
+        <v>3.7</v>
+      </c>
+      <c r="AA38">
+        <v>1.86</v>
+      </c>
+      <c r="AB38">
+        <v>1.91</v>
+      </c>
+      <c r="AC38">
+        <v>3.16</v>
+      </c>
+      <c r="AD38">
+        <v>1.31</v>
+      </c>
+      <c r="AE38">
         <v>1.07</v>
       </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.19</v>
-      </c>
-      <c r="Z38">
-        <v>3.8</v>
-      </c>
-      <c r="AA38">
+      <c r="AF38">
+        <v>1.7</v>
+      </c>
+      <c r="AG38">
+        <v>2.05</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.73</v>
       </c>
-      <c r="AB38">
-        <v>2.15</v>
-      </c>
-      <c r="AC38">
-        <v>2.61</v>
-      </c>
-      <c r="AD38">
-        <v>1.39</v>
-      </c>
-      <c r="AE38">
-        <v>1.12</v>
-      </c>
-      <c r="AF38">
-        <v>1.73</v>
-      </c>
-      <c r="AG38">
-        <v>2</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.25</v>
-      </c>
       <c r="AK38">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,69 +6662,69 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P39">
+        <v>5.15</v>
+      </c>
+      <c r="Q39">
+        <v>2.19</v>
+      </c>
+      <c r="R39">
+        <v>2.23</v>
+      </c>
+      <c r="S39">
+        <v>1.3</v>
+      </c>
+      <c r="T39">
+        <v>3.2</v>
+      </c>
+      <c r="U39">
+        <v>2.4</v>
+      </c>
+      <c r="V39">
+        <v>1.5</v>
+      </c>
+      <c r="W39">
+        <v>1.07</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.19</v>
+      </c>
+      <c r="Z39">
+        <v>3.8</v>
+      </c>
+      <c r="AA39">
+        <v>1.73</v>
+      </c>
+      <c r="AB39">
+        <v>2.15</v>
+      </c>
+      <c r="AC39">
+        <v>2.61</v>
+      </c>
+      <c r="AD39">
+        <v>1.39</v>
+      </c>
+      <c r="AE39">
+        <v>1.12</v>
+      </c>
+      <c r="AF39">
+        <v>1.73</v>
+      </c>
+      <c r="AG39">
         <v>2</v>
       </c>
-      <c r="Q39">
-        <v>3.9</v>
-      </c>
-      <c r="R39">
-        <v>2.25</v>
-      </c>
-      <c r="S39">
-        <v>1.38</v>
-      </c>
-      <c r="T39">
-        <v>3.08</v>
-      </c>
-      <c r="U39">
-        <v>2.78</v>
-      </c>
-      <c r="V39">
-        <v>1.43</v>
-      </c>
-      <c r="W39">
-        <v>1.06</v>
-      </c>
-      <c r="X39">
-        <v>1.05</v>
-      </c>
-      <c r="Y39">
-        <v>1.27</v>
-      </c>
-      <c r="Z39">
-        <v>3.7</v>
-      </c>
-      <c r="AA39">
-        <v>1.86</v>
-      </c>
-      <c r="AB39">
-        <v>1.91</v>
-      </c>
-      <c r="AC39">
-        <v>3.16</v>
-      </c>
-      <c r="AD39">
-        <v>1.31</v>
-      </c>
-      <c r="AE39">
-        <v>1.07</v>
-      </c>
-      <c r="AF39">
-        <v>1.7</v>
-      </c>
-      <c r="AG39">
-        <v>2.05</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G21">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -3439,31 +3439,31 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G43">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G46">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G57">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G61">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G62">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2606,10 +2606,10 @@
         <v>2.43</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U14">
         <v>2.15</v>
@@ -2621,7 +2621,7 @@
         <v>1.16</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.14</v>
@@ -2784,7 +2784,7 @@
         <v>1.11</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.17</v>
@@ -2932,10 +2932,10 @@
         <v>2.5</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U16">
         <v>2.26</v>
@@ -2947,7 +2947,7 @@
         <v>1.13</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.17</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G33">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="U35">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AA35">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC35">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AD35">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG35">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="Q36">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T36">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="U36">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AA36">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB36">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC36">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AD36">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G46">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL63">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>1.51</v>
+      </c>
+      <c r="O14">
+        <v>4.05</v>
+      </c>
+      <c r="P14">
+        <v>5.4</v>
+      </c>
+      <c r="Q14">
+        <v>1.97</v>
+      </c>
+      <c r="R14">
+        <v>2.5</v>
+      </c>
+      <c r="S14">
+        <v>1.3</v>
+      </c>
+      <c r="T14">
+        <v>3.22</v>
+      </c>
+      <c r="U14">
         <v>2.4</v>
       </c>
-      <c r="O14">
-        <v>3.55</v>
-      </c>
-      <c r="P14">
-        <v>2.55</v>
-      </c>
-      <c r="Q14">
-        <v>2.9</v>
-      </c>
-      <c r="R14">
-        <v>2.43</v>
-      </c>
-      <c r="S14">
-        <v>1.28</v>
-      </c>
-      <c r="T14">
-        <v>3.28</v>
-      </c>
-      <c r="U14">
-        <v>2.15</v>
-      </c>
       <c r="V14">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
+        <v>1.17</v>
+      </c>
+      <c r="Z14">
+        <v>4.3</v>
+      </c>
+      <c r="AA14">
+        <v>1.63</v>
+      </c>
+      <c r="AB14">
+        <v>2.12</v>
+      </c>
+      <c r="AC14">
+        <v>2.63</v>
+      </c>
+      <c r="AD14">
+        <v>1.42</v>
+      </c>
+      <c r="AE14">
         <v>1.14</v>
       </c>
-      <c r="Z14">
-        <v>4.7</v>
-      </c>
-      <c r="AA14">
-        <v>1.49</v>
-      </c>
-      <c r="AB14">
-        <v>2.34</v>
-      </c>
-      <c r="AC14">
-        <v>2.2</v>
-      </c>
-      <c r="AD14">
-        <v>1.57</v>
-      </c>
-      <c r="AE14">
-        <v>1.23</v>
-      </c>
       <c r="AF14">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AG14">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>1.64</v>
+        <v>2.38</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q15">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
         <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T15">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
         <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA15">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="AC15">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AD15">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AG15">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P16">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="R16">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S16">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="V16">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X16">
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z16">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="AA16">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB16">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AC16">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AD16">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE16">
+        <v>1.23</v>
+      </c>
+      <c r="AF16">
+        <v>1.42</v>
+      </c>
+      <c r="AG16">
+        <v>2.5</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.22</v>
       </c>
-      <c r="AF16">
-        <v>1.41</v>
-      </c>
-      <c r="AG16">
-        <v>2.55</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.21</v>
-      </c>
       <c r="AK16">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
         <v>3.25</v>
@@ -3270,7 +3270,7 @@
         <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,28 +3279,28 @@
         <v>1.16</v>
       </c>
       <c r="Z18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA18">
         <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AC18">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD18">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
         <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AG18">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,37 +3406,37 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q19">
         <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="V19">
         <v>1.5</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.15</v>
@@ -3445,19 +3445,19 @@
         <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB19">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC19">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
         <v>1.46</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,37 +3569,37 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q20">
         <v>3.3</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="V20">
         <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20">
         <v>1.15</v>
@@ -3608,19 +3608,19 @@
         <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC20">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AD20">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
         <v>1.46</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,22 +3732,22 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O21">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="Q21">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T21">
         <v>3.25</v>
@@ -3759,7 +3759,7 @@
         <v>1.53</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,28 +3768,28 @@
         <v>1.16</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA21">
         <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AC21">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD21">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
         <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG21">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G46">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,52 +3406,52 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
         <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
         <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AC19">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AD19">
         <v>1.42</v>
@@ -3460,10 +3460,10 @@
         <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG19">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,37 +3569,37 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
         <v>3.3</v>
       </c>
       <c r="R20">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="V20">
         <v>1.5</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.15</v>
@@ -3608,19 +3608,19 @@
         <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB20">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC20">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AD20">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
         <v>1.46</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S21">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC21">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG21">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G46">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G57">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="O3">
         <v>2.8</v>
@@ -807,34 +807,34 @@
         <v>3.65</v>
       </c>
       <c r="Q3">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="S3">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="T3">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y3">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z3">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="AA3">
         <v>2.66</v>
@@ -843,19 +843,19 @@
         <v>1.46</v>
       </c>
       <c r="AC3">
-        <v>5.16</v>
+        <v>4.6</v>
       </c>
       <c r="AD3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
         <v>2.2</v>
       </c>
       <c r="AG3">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>5.14</v>
+        <v>3.9</v>
       </c>
       <c r="Q4">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="R4">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
         <v>1.36</v>
@@ -982,43 +982,43 @@
         <v>2.85</v>
       </c>
       <c r="U4">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC4">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AD4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="O27">
         <v>3</v>
@@ -4722,7 +4722,7 @@
         <v>3.65</v>
       </c>
       <c r="R27">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
         <v>1.4</v>
@@ -4731,16 +4731,16 @@
         <v>2.7</v>
       </c>
       <c r="U27">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="V27">
         <v>1.29</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y27">
         <v>1.36</v>
@@ -4749,25 +4749,25 @@
         <v>2.7</v>
       </c>
       <c r="AA27">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AB27">
         <v>1.62</v>
       </c>
       <c r="AC27">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AD27">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
         <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G33">
@@ -5854,10 +5854,10 @@
         <v>4.55</v>
       </c>
       <c r="O34">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q34">
         <v>4.8</v>
@@ -5872,13 +5872,13 @@
         <v>3</v>
       </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.05</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P35">
         <v>3.8</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O36">
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="Q36">
         <v>2.6</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G61">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G62">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q22">
         <v>2.45</v>
@@ -3913,7 +3913,7 @@
         <v>1.35</v>
       </c>
       <c r="T22">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
         <v>2.65</v>
@@ -3922,7 +3922,7 @@
         <v>1.42</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -3943,7 +3943,7 @@
         <v>3.4</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="O25">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P25">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
       </c>
       <c r="R25">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S25">
         <v>1.45</v>
@@ -4408,10 +4408,10 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.09</v>
@@ -4441,7 +4441,7 @@
         <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q51">
-        <v>1.73</v>
+        <v>2.52</v>
       </c>
       <c r="R51">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="V51">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="Z51">
-        <v>3.98</v>
+        <v>3.08</v>
       </c>
       <c r="AA51">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AC51">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>3.44</v>
+        <v>1.81</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.52</v>
+        <v>1.73</v>
       </c>
       <c r="R52">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T52">
-        <v>2.88</v>
+        <v>3.36</v>
       </c>
       <c r="U52">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="V52">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="W52">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>3.08</v>
+        <v>3.98</v>
       </c>
       <c r="AA52">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB52">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AC52">
-        <v>3.34</v>
+        <v>2.59</v>
       </c>
       <c r="AD52">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AG52">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK52">
-        <v>1.81</v>
+        <v>3.44</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -807,13 +807,13 @@
         <v>3.65</v>
       </c>
       <c r="Q3">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="R3">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="S3">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="T3">
         <v>2.18</v>
@@ -822,10 +822,10 @@
         <v>3.4</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1.08</v>
@@ -843,19 +843,19 @@
         <v>1.46</v>
       </c>
       <c r="AC3">
-        <v>4.6</v>
+        <v>5.16</v>
       </c>
       <c r="AD3">
         <v>1.13</v>
       </c>
       <c r="AE3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
         <v>2.2</v>
       </c>
       <c r="AG3">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
         <v>1.6</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2265,61 +2265,61 @@
         </is>
       </c>
       <c r="N12">
+        <v>1.95</v>
+      </c>
+      <c r="O12">
+        <v>2.85</v>
+      </c>
+      <c r="P12">
+        <v>3.9</v>
+      </c>
+      <c r="Q12">
+        <v>2.73</v>
+      </c>
+      <c r="R12">
         <v>1.79</v>
       </c>
-      <c r="O12">
-        <v>2.95</v>
-      </c>
-      <c r="P12">
-        <v>4.75</v>
-      </c>
-      <c r="Q12">
-        <v>2.45</v>
-      </c>
-      <c r="R12">
-        <v>1.83</v>
-      </c>
       <c r="S12">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U12">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V12">
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z12">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AA12">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AB12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC12">
         <v>5</v>
       </c>
       <c r="AD12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AG12">
         <v>1.57</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>7.5</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R17">
         <v>3.1</v>
@@ -3098,10 +3098,10 @@
         <v>1.16</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="U17">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="V17">
         <v>2</v>
@@ -3125,7 +3125,7 @@
         <v>3.14</v>
       </c>
       <c r="AC17">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AD17">
         <v>1.98</v>
@@ -3137,7 +3137,7 @@
         <v>1.59</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK17">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3264,13 +3264,13 @@
         <v>3.25</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P19">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
         <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3584,10 +3584,10 @@
         <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U20">
         <v>2.36</v>
@@ -3596,7 +3596,7 @@
         <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3614,7 +3614,7 @@
         <v>2.16</v>
       </c>
       <c r="AC20">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD20">
         <v>1.42</v>
@@ -4550,10 +4550,10 @@
         <v>1.17</v>
       </c>
       <c r="O26">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="P26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q26">
         <v>1.49</v>
@@ -4562,19 +4562,19 @@
         <v>3.4</v>
       </c>
       <c r="S26">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T26">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="U26">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="V26">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W26">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X26">
         <v>1</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK26">
         <v>4.5</v>
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="V37">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
+        <v>1.22</v>
+      </c>
+      <c r="Z37">
+        <v>4</v>
+      </c>
+      <c r="AA37">
+        <v>1.72</v>
+      </c>
+      <c r="AB37">
+        <v>2.08</v>
+      </c>
+      <c r="AC37">
+        <v>2.64</v>
+      </c>
+      <c r="AD37">
+        <v>1.38</v>
+      </c>
+      <c r="AE37">
+        <v>1.11</v>
+      </c>
+      <c r="AF37">
+        <v>1.62</v>
+      </c>
+      <c r="AG37">
+        <v>2.2</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.25</v>
       </c>
-      <c r="Z37">
-        <v>3.6</v>
-      </c>
-      <c r="AA37">
-        <v>1.83</v>
-      </c>
-      <c r="AB37">
-        <v>1.95</v>
-      </c>
-      <c r="AC37">
-        <v>3.15</v>
-      </c>
-      <c r="AD37">
-        <v>1.34</v>
-      </c>
-      <c r="AE37">
-        <v>1.1</v>
-      </c>
-      <c r="AF37">
-        <v>1.65</v>
-      </c>
-      <c r="AG37">
-        <v>2.06</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.35</v>
-      </c>
       <c r="AK37">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="U38">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="V38">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA38">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AB38">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC38">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE38">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P39">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="Q39">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V39">
+        <v>1.61</v>
+      </c>
+      <c r="W39">
+        <v>1.13</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.14</v>
+      </c>
+      <c r="Z39">
+        <v>5</v>
+      </c>
+      <c r="AA39">
         <v>1.5</v>
       </c>
-      <c r="W39">
-        <v>1.07</v>
-      </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
-        <v>1.19</v>
-      </c>
-      <c r="Z39">
-        <v>3.8</v>
-      </c>
-      <c r="AA39">
-        <v>1.73</v>
-      </c>
       <c r="AB39">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC39">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="AD39">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8622,61 +8622,61 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O51">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q51">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="R51">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
         <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U51">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z51">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA51">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB51">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE51">
         <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
         <v>1.9</v>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R52">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S52">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.98</v>
+        <v>4.16</v>
       </c>
       <c r="AA52">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB52">
+        <v>2.07</v>
+      </c>
+      <c r="AC52">
+        <v>2.62</v>
+      </c>
+      <c r="AD52">
+        <v>1.38</v>
+      </c>
+      <c r="AE52">
+        <v>1.15</v>
+      </c>
+      <c r="AF52">
         <v>2.05</v>
       </c>
-      <c r="AC52">
-        <v>2.59</v>
-      </c>
-      <c r="AD52">
-        <v>1.4</v>
-      </c>
-      <c r="AE52">
-        <v>1.12</v>
-      </c>
-      <c r="AF52">
-        <v>2.1</v>
-      </c>
       <c r="AG52">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK52">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,77 +8951,77 @@
         <v>1.65</v>
       </c>
       <c r="O53">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="P53">
         <v>3.6</v>
       </c>
       <c r="Q53">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="U53">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="V53">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W53">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z53">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA53">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB53">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC53">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD53">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AE53">
+        <v>1.08</v>
+      </c>
+      <c r="AF53">
+        <v>1.79</v>
+      </c>
+      <c r="AG53">
+        <v>1.9</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
         <v>1.21</v>
       </c>
-      <c r="AF53">
-        <v>1.57</v>
-      </c>
-      <c r="AG53">
-        <v>2.15</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.16</v>
-      </c>
       <c r="AK53">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G57">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G61">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G62">

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
         <v>1.88</v>
@@ -1163,25 +1163,25 @@
         <v>4.25</v>
       </c>
       <c r="AA5">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AB5">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AC5">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AD5">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AG5">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="V13">
         <v>1.57</v>
@@ -2464,13 +2464,13 @@
         <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA13">
         <v>1.66</v>
       </c>
       <c r="AB13">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC13">
         <v>2.5</v>
@@ -2479,7 +2479,7 @@
         <v>1.45</v>
       </c>
       <c r="AE13">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
         <v>1.57</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="O14">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P14">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q14">
         <v>1.97</v>
@@ -2606,28 +2606,28 @@
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA14">
         <v>1.63</v>
@@ -2642,13 +2642,13 @@
         <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
         <v>1.72</v>
       </c>
       <c r="AG14">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R15">
         <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
         <v>1.13</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AA15">
         <v>1.44</v>
@@ -2799,7 +2799,7 @@
         <v>2.55</v>
       </c>
       <c r="AC15">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AD15">
         <v>1.6</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
         <v>3.55</v>
       </c>
       <c r="P16">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="Q16">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="R16">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="S16">
         <v>1.28</v>
@@ -2938,13 +2938,13 @@
         <v>3.28</v>
       </c>
       <c r="U16">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="V16">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2953,22 +2953,22 @@
         <v>1.14</v>
       </c>
       <c r="Z16">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AA16">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AC16">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD16">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
         <v>1.42</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,52 +3406,52 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB19">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AC19">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD19">
         <v>1.42</v>
@@ -3460,10 +3460,10 @@
         <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG19">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,37 +3569,37 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q20">
         <v>3.3</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S20">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="V20">
         <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20">
         <v>1.15</v>
@@ -3608,19 +3608,19 @@
         <v>4.2</v>
       </c>
       <c r="AA20">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC20">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AD20">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
         <v>1.46</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P21">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB21">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC21">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="O22">
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q22">
         <v>2.45</v>
@@ -3940,10 +3940,10 @@
         <v>1.86</v>
       </c>
       <c r="AC22">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AD22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
         <v>1.86</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="O25">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="P25">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R25">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S25">
         <v>1.45</v>
@@ -4417,16 +4417,16 @@
         <v>1.09</v>
       </c>
       <c r="Y25">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z25">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AA25">
         <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
         <v>4.2</v>
@@ -4441,7 +4441,7 @@
         <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5860,22 +5860,22 @@
         <v>1.65</v>
       </c>
       <c r="Q34">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
         <v>1.06</v>
@@ -5887,19 +5887,19 @@
         <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA34">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
         <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE34">
         <v>1.11</v>
@@ -5924,7 +5924,7 @@
         <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O36">
         <v>3.5</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="P47">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="Q47">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="S47">
         <v>1.15</v>
@@ -7991,10 +7991,10 @@
         <v>4.55</v>
       </c>
       <c r="U47">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="V47">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="W47">
         <v>1.29</v>
@@ -8003,31 +8003,31 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Z47">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB47">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="AC47">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AD47">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AE47">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF47">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AG47">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="N48">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O48">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="P48">
         <v>1.28</v>
@@ -8148,28 +8148,28 @@
         <v>2.8</v>
       </c>
       <c r="S48">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="T48">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V48">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W48">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z48">
-        <v>5.7</v>
+        <v>6.25</v>
       </c>
       <c r="AA48">
         <v>1.36</v>
@@ -8181,16 +8181,16 @@
         <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE48">
         <v>1.33</v>
       </c>
       <c r="AF48">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK48">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-15 18:15:00</t>
+          <t>2026-09-15 18:30:00</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
         <v>3.3</v>
       </c>
       <c r="P51">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q51">
         <v>2.37</v>
@@ -8637,7 +8637,7 @@
         <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T51">
         <v>2.9</v>
@@ -8646,10 +8646,10 @@
         <v>2.81</v>
       </c>
       <c r="V51">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8664,7 +8664,7 @@
         <v>2.02</v>
       </c>
       <c r="AB51">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC51">
         <v>3.2</v>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8809,13 +8809,13 @@
         <v>2.4</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.22</v>
@@ -8839,10 +8839,10 @@
         <v>1.15</v>
       </c>
       <c r="AF52">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG52">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK52">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>3.1</v>
       </c>
       <c r="Q54">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R54">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
         <v>1.25</v>
@@ -9132,10 +9132,10 @@
         <v>3.4</v>
       </c>
       <c r="U54">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="V54">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W54">
         <v>1.13</v>
@@ -10578,34 +10578,34 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q63">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="R63">
         <v>2.37</v>
       </c>
       <c r="S63">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T63">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="U63">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V63">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
         <v>1</v>
@@ -10617,10 +10617,10 @@
         <v>3.84</v>
       </c>
       <c r="AA63">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB63">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AC63">
         <v>2.7</v>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
         <v>1.91</v>

--- a/jogos_2026-09-15.xlsx
+++ b/jogos_2026-09-15.xlsx
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
         <v>1.88</v>
@@ -3086,7 +3086,7 @@
         <v>5.75</v>
       </c>
       <c r="P17">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q17">
         <v>1.56</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK17">
         <v>3.3</v>
@@ -3427,7 +3427,7 @@
         <v>3.18</v>
       </c>
       <c r="U19">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
         <v>1.5</v>
@@ -3451,7 +3451,7 @@
         <v>2.16</v>
       </c>
       <c r="AC19">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD19">
         <v>1.42</v>
@@ -3753,10 +3753,10 @@
         <v>3.25</v>
       </c>
       <c r="U21">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V21">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W21">
         <v>1.13</v>
@@ -3943,7 +3943,7 @@
         <v>3.41</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE22">
         <v>1.1</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O25">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
         <v>2.05</v>
@@ -4408,7 +4408,7 @@
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -8136,10 +8136,10 @@
         <v>8</v>
       </c>
       <c r="O48">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="P48">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Q48">
         <v>6.5</v>
@@ -8151,13 +8151,13 @@
         <v>1.14</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U48">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V48">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W48">
         <v>1.2</v>
@@ -8181,7 +8181,7 @@
         <v>1.95</v>
       </c>
       <c r="AD48">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AE48">
         <v>1.33</v>
@@ -8190,7 +8190,7 @@
         <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
